--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,6 +1168,1030 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129670198</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>713600</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6365720</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129670196</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>713577</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6365739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129670687</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57857</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>713554</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6365628</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129670200</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>713622</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6365687</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129670206</v>
+      </c>
+      <c r="B10" t="n">
+        <v>107645</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>713659</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6365643</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129670230</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>713532</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6365745</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129670203</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>713629</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6365679</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129670204</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>713659</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365643</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129670194</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Buttle, Altajme 1:35, A53584, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>713561</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6365747</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Buttle</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>kalbarrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129670687</v>
       </c>
       <c r="B8" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107645</v>
+        <v>107674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98761</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129670687</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107674</v>
+        <v>107686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129670687</v>
       </c>
       <c r="B8" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107686</v>
+        <v>107687</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107687</v>
+        <v>107692</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98803</v>
+        <v>98808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107692</v>
+        <v>107696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson, Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson, Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107696</v>
+        <v>107698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107698</v>
+        <v>107708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107708</v>
+        <v>107712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>129670687</v>
       </c>
       <c r="B8" t="n">
-        <v>57866</v>
+        <v>57869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson</t>
+          <t>Jörgen Petersson, Gun Ingmansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107712</v>
+        <v>107715</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1173,7 +1173,7 @@
         <v>129670198</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>129670196</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Gun Ingmansson</t>
+          <t>Gun Ingmansson, Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
         <v>129670200</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129670206</v>
       </c>
       <c r="B10" t="n">
-        <v>107715</v>
+        <v>107716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>129670230</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>129670203</v>
       </c>
       <c r="B12" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>129670204</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>129670194</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 53584-2025 artfynd.xlsx
+++ b/artfynd/A 53584-2025 artfynd.xlsx
@@ -1409,7 +1409,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
